--- a/src/wordle_log.xlsx
+++ b/src/wordle_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -501,7 +501,7 @@
           <t>S</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -514,29 +514,29 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -547,227 +547,224 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JETTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="n">
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+    </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>T</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ABOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="n">
         <v>3</v>
       </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>E</t>
         </is>
@@ -775,98 +772,98 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>L</t>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="n">
         <v>4</v>
       </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
@@ -874,34 +871,541 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>FINCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="n">
         <v>4</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PRONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DINER</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TRIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>7</v>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>7</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EDICT</t>
         </is>
       </c>
     </row>

--- a/src/wordle_log.xlsx
+++ b/src/wordle_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="n">
         <v>7</v>
@@ -1406,6 +1407,8394 @@
       <c r="C39" t="inlineStr">
         <is>
           <t>EDICT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>8</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>REPAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>9</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>9</v>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>9</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BIDDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>10</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>10</v>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>10</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>10</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BIDDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>11</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>11</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>11</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>11</v>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>11</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>WHINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>12</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>12</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>12</v>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>12</v>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>12</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>PLUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>13</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>13</v>
+      </c>
+      <c r="B78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>13</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>QUACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>14</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>14</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2</v>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>14</v>
+      </c>
+      <c r="B83" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>14</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>QUACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>15</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>15</v>
+      </c>
+      <c r="B88" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>15</v>
+      </c>
+      <c r="B89" t="n">
+        <v>4</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>15</v>
+      </c>
+      <c r="B90" t="n">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>15</v>
+      </c>
+      <c r="B91" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>16</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>16</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>16</v>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>16</v>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>16</v>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>16</v>
+      </c>
+      <c r="B98" t="n">
+        <v>6</v>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>17</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>18</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>18</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>18</v>
+      </c>
+      <c r="B104" t="n">
+        <v>3</v>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>18</v>
+      </c>
+      <c r="B105" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>18</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>QUALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>19</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>19</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>19</v>
+      </c>
+      <c r="B110" t="n">
+        <v>3</v>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>19</v>
+      </c>
+      <c r="B111" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>19</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>QUALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>20</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>20</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>20</v>
+      </c>
+      <c r="B116" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>21</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>21</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>21</v>
+      </c>
+      <c r="B120" t="n">
+        <v>3</v>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>21</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ISSUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122"/>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>22</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>22</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>22</v>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>22</v>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>22</v>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>22</v>
+      </c>
+      <c r="B128" t="n">
+        <v>6</v>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>22</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>INPUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>23</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>23</v>
+      </c>
+      <c r="B132" t="n">
+        <v>2</v>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>23</v>
+      </c>
+      <c r="B133" t="n">
+        <v>3</v>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>23</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BASTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>24</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>24</v>
+      </c>
+      <c r="B137" t="n">
+        <v>2</v>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>24</v>
+      </c>
+      <c r="B138" t="n">
+        <v>3</v>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>24</v>
+      </c>
+      <c r="B139" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>24</v>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>24</v>
+      </c>
+      <c r="B141" t="n">
+        <v>6</v>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>24</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>HONOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>25</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>25</v>
+      </c>
+      <c r="B145" t="n">
+        <v>2</v>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>25</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>25</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4</v>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>25</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SLUMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="149"/>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>26</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>26</v>
+      </c>
+      <c r="B151" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>26</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>26</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>OUGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="154"/>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>27</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>27</v>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>27</v>
+      </c>
+      <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>27</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>27</v>
+      </c>
+      <c r="B159" t="n">
+        <v>5</v>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>27</v>
+      </c>
+      <c r="B160" t="n">
+        <v>6</v>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>27</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>TERRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162"/>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>28</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>28</v>
+      </c>
+      <c r="B164" t="n">
+        <v>2</v>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>28</v>
+      </c>
+      <c r="B165" t="n">
+        <v>3</v>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>28</v>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>28</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>28</v>
+      </c>
+      <c r="B168" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>28</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>TERRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="170"/>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>29</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>29</v>
+      </c>
+      <c r="B172" t="n">
+        <v>2</v>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>29</v>
+      </c>
+      <c r="B173" t="n">
+        <v>3</v>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>29</v>
+      </c>
+      <c r="B174" t="n">
+        <v>4</v>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F174" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>29</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F175" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>29</v>
+      </c>
+      <c r="B176" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F176" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>29</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TERRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="178"/>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>30</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F179" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>30</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2</v>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>30</v>
+      </c>
+      <c r="B181" t="n">
+        <v>3</v>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>30</v>
+      </c>
+      <c r="B182" t="n">
+        <v>4</v>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F182" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>30</v>
+      </c>
+      <c r="B183" t="n">
+        <v>5</v>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F183" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>30</v>
+      </c>
+      <c r="B184" t="n">
+        <v>6</v>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F184" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>30</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>TERRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="186"/>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>31</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>31</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2</v>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G188" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>31</v>
+      </c>
+      <c r="B189" t="n">
+        <v>3</v>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>31</v>
+      </c>
+      <c r="B190" t="n">
+        <v>4</v>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G190" s="3" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>31</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ABACK</t>
+        </is>
+      </c>
+    </row>
+    <row r="192"/>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>32</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>32</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2</v>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>32</v>
+      </c>
+      <c r="B195" t="n">
+        <v>3</v>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>32</v>
+      </c>
+      <c r="B196" t="n">
+        <v>4</v>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>32</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ODDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="198"/>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>33</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F199" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>33</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2</v>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="201"/>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>34</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>34</v>
+      </c>
+      <c r="B203" t="n">
+        <v>2</v>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G203" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>34</v>
+      </c>
+      <c r="B204" t="n">
+        <v>3</v>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>34</v>
+      </c>
+      <c r="B205" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>34</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SHIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="207"/>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>35</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F208" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>35</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2</v>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G209" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>35</v>
+      </c>
+      <c r="B210" t="n">
+        <v>3</v>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>35</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>TENTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="212"/>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>36</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>36</v>
+      </c>
+      <c r="B214" t="n">
+        <v>2</v>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>36</v>
+      </c>
+      <c r="B215" t="n">
+        <v>3</v>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G215" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>36</v>
+      </c>
+      <c r="B216" t="n">
+        <v>4</v>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G216" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>36</v>
+      </c>
+      <c r="B217" t="n">
+        <v>5</v>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G217" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>36</v>
+      </c>
+      <c r="B218" t="n">
+        <v>6</v>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G218" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>36</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>MISSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="220"/>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>37</v>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G221" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>37</v>
+      </c>
+      <c r="B222" t="n">
+        <v>2</v>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="223"/>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>38</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>38</v>
+      </c>
+      <c r="B225" t="n">
+        <v>2</v>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>38</v>
+      </c>
+      <c r="B226" t="n">
+        <v>3</v>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G226" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>38</v>
+      </c>
+      <c r="B227" t="n">
+        <v>4</v>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>38</v>
+      </c>
+      <c r="B228" t="n">
+        <v>5</v>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G228" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>38</v>
+      </c>
+      <c r="B229" t="n">
+        <v>6</v>
+      </c>
+      <c r="C229" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G229" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>38</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>RIPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="231"/>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>39</v>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F232" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>39</v>
+      </c>
+      <c r="B233" t="n">
+        <v>2</v>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>39</v>
+      </c>
+      <c r="B234" t="n">
+        <v>3</v>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G234" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>39</v>
+      </c>
+      <c r="B235" t="n">
+        <v>4</v>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>39</v>
+      </c>
+      <c r="B236" t="n">
+        <v>5</v>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>39</v>
+      </c>
+      <c r="B237" t="n">
+        <v>6</v>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>39</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>RERUN</t>
+        </is>
+      </c>
+    </row>
+    <row r="239"/>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>40</v>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F240" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>40</v>
+      </c>
+      <c r="B241" t="n">
+        <v>2</v>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>40</v>
+      </c>
+      <c r="B242" t="n">
+        <v>3</v>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G242" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>40</v>
+      </c>
+      <c r="B243" t="n">
+        <v>4</v>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="244"/>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>41</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F245" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>41</v>
+      </c>
+      <c r="B246" t="n">
+        <v>2</v>
+      </c>
+      <c r="C246" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>41</v>
+      </c>
+      <c r="B247" t="n">
+        <v>3</v>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>41</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>HALVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="249"/>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>42</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F250" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G250" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>42</v>
+      </c>
+      <c r="B251" t="n">
+        <v>2</v>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F251" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G251" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>42</v>
+      </c>
+      <c r="B252" t="n">
+        <v>3</v>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>42</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>CRYPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="254"/>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>43</v>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E255" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F255" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G255" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="256"/>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>44</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E257" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>44</v>
+      </c>
+      <c r="B258" t="n">
+        <v>2</v>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F258" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>44</v>
+      </c>
+      <c r="B259" t="n">
+        <v>3</v>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>44</v>
+      </c>
+      <c r="B260" t="n">
+        <v>4</v>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>44</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SCREW</t>
+        </is>
+      </c>
+    </row>
+    <row r="262"/>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>45</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E263" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>45</v>
+      </c>
+      <c r="B264" t="n">
+        <v>2</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E264" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F264" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>45</v>
+      </c>
+      <c r="B265" t="n">
+        <v>3</v>
+      </c>
+      <c r="C265" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>45</v>
+      </c>
+      <c r="B266" t="n">
+        <v>4</v>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>45</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SCREW</t>
+        </is>
+      </c>
+    </row>
+    <row r="268"/>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>46</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E269" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F269" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G269" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>46</v>
+      </c>
+      <c r="B270" t="n">
+        <v>2</v>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E270" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G270" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>46</v>
+      </c>
+      <c r="B271" t="n">
+        <v>3</v>
+      </c>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>46</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>FUNGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>47</v>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E274" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F274" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>47</v>
+      </c>
+      <c r="B275" t="n">
+        <v>2</v>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E275" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G275" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="276"/>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>48</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E277" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F277" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G277" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>48</v>
+      </c>
+      <c r="B278" t="n">
+        <v>2</v>
+      </c>
+      <c r="C278" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E278" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G278" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>48</v>
+      </c>
+      <c r="B279" t="n">
+        <v>3</v>
+      </c>
+      <c r="C279" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F279" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>48</v>
+      </c>
+      <c r="B280" t="n">
+        <v>4</v>
+      </c>
+      <c r="C280" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F280" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>48</v>
+      </c>
+      <c r="B281" t="n">
+        <v>5</v>
+      </c>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>48</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>PRIVY</t>
+        </is>
+      </c>
+    </row>
+    <row r="283"/>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>49</v>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+      <c r="C284" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E284" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F284" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G284" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="285"/>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>50</v>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D286" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E286" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G286" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>50</v>
+      </c>
+      <c r="B287" t="n">
+        <v>2</v>
+      </c>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D287" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>50</v>
+      </c>
+      <c r="B288" t="n">
+        <v>3</v>
+      </c>
+      <c r="C288" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>50</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>HUSSY</t>
+        </is>
+      </c>
+    </row>
+    <row r="290"/>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>51</v>
+      </c>
+      <c r="B291" t="n">
+        <v>1</v>
+      </c>
+      <c r="C291" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D291" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F291" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>51</v>
+      </c>
+      <c r="B292" t="n">
+        <v>2</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D292" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E292" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G292" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>51</v>
+      </c>
+      <c r="B293" t="n">
+        <v>3</v>
+      </c>
+      <c r="C293" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G293" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>51</v>
+      </c>
+      <c r="B294" t="n">
+        <v>4</v>
+      </c>
+      <c r="C294" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>51</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>COVEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="296"/>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>52</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E297" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>52</v>
+      </c>
+      <c r="B298" t="n">
+        <v>2</v>
+      </c>
+      <c r="C298" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>52</v>
+      </c>
+      <c r="B299" t="n">
+        <v>3</v>
+      </c>
+      <c r="C299" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F299" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>52</v>
+      </c>
+      <c r="B300" t="n">
+        <v>4</v>
+      </c>
+      <c r="C300" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F300" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>52</v>
+      </c>
+      <c r="B301" t="n">
+        <v>5</v>
+      </c>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F301" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>52</v>
+      </c>
+      <c r="B302" t="n">
+        <v>6</v>
+      </c>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F302" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>52</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SCREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="304"/>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>53</v>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>53</v>
+      </c>
+      <c r="B306" t="n">
+        <v>2</v>
+      </c>
+      <c r="C306" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>53</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>AISLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="308"/>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>54</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G309" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="310"/>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>55</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F311" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G311" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>55</v>
+      </c>
+      <c r="B312" t="n">
+        <v>2</v>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F312" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>55</v>
+      </c>
+      <c r="B313" t="n">
+        <v>3</v>
+      </c>
+      <c r="C313" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G313" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>55</v>
+      </c>
+      <c r="B314" t="n">
+        <v>4</v>
+      </c>
+      <c r="C314" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E314" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>55</v>
+      </c>
+      <c r="B315" t="n">
+        <v>5</v>
+      </c>
+      <c r="C315" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E315" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G315" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>55</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>LOCAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="317"/>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>56</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E318" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F318" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G318" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>56</v>
+      </c>
+      <c r="B319" t="n">
+        <v>2</v>
+      </c>
+      <c r="C319" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E319" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G319" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>56</v>
+      </c>
+      <c r="B320" t="n">
+        <v>3</v>
+      </c>
+      <c r="C320" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E320" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F320" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G320" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>56</v>
+      </c>
+      <c r="B321" t="n">
+        <v>4</v>
+      </c>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G321" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>56</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>PLACE</t>
+        </is>
+      </c>
+    </row>
+    <row r="323"/>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>57</v>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F324" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>57</v>
+      </c>
+      <c r="B325" t="n">
+        <v>2</v>
+      </c>
+      <c r="C325" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E325" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G325" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>57</v>
+      </c>
+      <c r="B326" t="n">
+        <v>3</v>
+      </c>
+      <c r="C326" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E326" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G326" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>57</v>
+      </c>
+      <c r="B327" t="n">
+        <v>4</v>
+      </c>
+      <c r="C327" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E327" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G327" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>57</v>
+      </c>
+      <c r="B328" t="n">
+        <v>5</v>
+      </c>
+      <c r="C328" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E328" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G328" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>57</v>
+      </c>
+      <c r="B329" t="n">
+        <v>6</v>
+      </c>
+      <c r="C329" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E329" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G329" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>57</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>ROWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="331"/>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>58</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E332" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G332" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>58</v>
+      </c>
+      <c r="B333" t="n">
+        <v>2</v>
+      </c>
+      <c r="C333" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E333" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G333" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>58</v>
+      </c>
+      <c r="B334" t="n">
+        <v>3</v>
+      </c>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F334" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>58</v>
+      </c>
+      <c r="B335" t="n">
+        <v>4</v>
+      </c>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F335" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>58</v>
+      </c>
+      <c r="B336" t="n">
+        <v>5</v>
+      </c>
+      <c r="C336" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F336" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>58</v>
+      </c>
+      <c r="B337" t="n">
+        <v>6</v>
+      </c>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F337" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>58</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>STOKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="339"/>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>59</v>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C340" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D340" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G340" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>59</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2</v>
+      </c>
+      <c r="C341" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D341" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E341" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G341" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="342"/>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>60</v>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F343" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G343" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>60</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2</v>
+      </c>
+      <c r="C344" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G344" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>60</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>ABODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="346"/>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>61</v>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D347" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E347" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F347" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>61</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2</v>
+      </c>
+      <c r="C348" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D348" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E348" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>61</v>
+      </c>
+      <c r="B349" t="n">
+        <v>3</v>
+      </c>
+      <c r="C349" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E349" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>61</v>
+      </c>
+      <c r="B350" t="n">
+        <v>4</v>
+      </c>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E350" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>61</v>
+      </c>
+      <c r="B351" t="n">
+        <v>5</v>
+      </c>
+      <c r="C351" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E351" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F351" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G351" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>61</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>TWEED</t>
+        </is>
+      </c>
+    </row>
+    <row r="353"/>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>62</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D354" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F354" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>62</v>
+      </c>
+      <c r="B355" t="n">
+        <v>2</v>
+      </c>
+      <c r="C355" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D355" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E355" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F355" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G355" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>62</v>
+      </c>
+      <c r="B356" t="n">
+        <v>3</v>
+      </c>
+      <c r="C356" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D356" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E356" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G356" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>62</v>
+      </c>
+      <c r="B357" t="n">
+        <v>4</v>
+      </c>
+      <c r="C357" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D357" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E357" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F357" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G357" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>62</v>
+      </c>
+      <c r="B358" t="n">
+        <v>5</v>
+      </c>
+      <c r="C358" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D358" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E358" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G358" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>62</v>
+      </c>
+      <c r="B359" t="n">
+        <v>6</v>
+      </c>
+      <c r="C359" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E359" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G359" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>62</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>OCTET</t>
+        </is>
+      </c>
+    </row>
+    <row r="361"/>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>63</v>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F362" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="363"/>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>64</v>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G364" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>64</v>
+      </c>
+      <c r="B365" t="n">
+        <v>2</v>
+      </c>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D365" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>64</v>
+      </c>
+      <c r="B366" t="n">
+        <v>3</v>
+      </c>
+      <c r="C366" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F366" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G366" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>64</v>
+      </c>
+      <c r="B367" t="n">
+        <v>4</v>
+      </c>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F367" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G367" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>64</v>
+      </c>
+      <c r="B368" t="n">
+        <v>5</v>
+      </c>
+      <c r="C368" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F368" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G368" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>64</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>STORY</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>65</v>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E371" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F371" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G371" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>65</v>
+      </c>
+      <c r="B372" t="n">
+        <v>2</v>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E372" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G372" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>65</v>
+      </c>
+      <c r="B373" t="n">
+        <v>3</v>
+      </c>
+      <c r="C373" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D373" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E373" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F373" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G373" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>65</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>EAGLE</t>
         </is>
       </c>
     </row>

--- a/src/wordle_log.xlsx
+++ b/src/wordle_log.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9684,6 +9684,7 @@
         </is>
       </c>
     </row>
+    <row r="370"/>
     <row r="371">
       <c r="A371" t="n">
         <v>65</v>
@@ -9795,6 +9796,2871 @@
       <c r="C374" t="inlineStr">
         <is>
           <t>EAGLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="375"/>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>66</v>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F376" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G376" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>66</v>
+      </c>
+      <c r="B377" t="n">
+        <v>2</v>
+      </c>
+      <c r="C377" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D377" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E377" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>66</v>
+      </c>
+      <c r="B378" t="n">
+        <v>3</v>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E378" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G378" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>66</v>
+      </c>
+      <c r="B379" t="n">
+        <v>4</v>
+      </c>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F379" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G379" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>66</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>TODDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>67</v>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D382" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E382" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G382" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>67</v>
+      </c>
+      <c r="B383" t="n">
+        <v>2</v>
+      </c>
+      <c r="C383" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>67</v>
+      </c>
+      <c r="B384" t="n">
+        <v>3</v>
+      </c>
+      <c r="C384" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F384" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G384" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>67</v>
+      </c>
+      <c r="B385" t="n">
+        <v>4</v>
+      </c>
+      <c r="C385" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D385" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E385" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F385" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G385" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>67</v>
+      </c>
+      <c r="B386" t="n">
+        <v>5</v>
+      </c>
+      <c r="C386" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G386" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>67</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>STINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="388"/>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>68</v>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+      <c r="C389" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D389" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E389" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G389" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>68</v>
+      </c>
+      <c r="B390" t="n">
+        <v>2</v>
+      </c>
+      <c r="C390" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="391"/>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>69</v>
+      </c>
+      <c r="B392" t="n">
+        <v>1</v>
+      </c>
+      <c r="C392" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E392" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F392" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>69</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2</v>
+      </c>
+      <c r="C393" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D393" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E393" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>69</v>
+      </c>
+      <c r="B394" t="n">
+        <v>3</v>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E394" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G394" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>69</v>
+      </c>
+      <c r="B395" t="n">
+        <v>4</v>
+      </c>
+      <c r="C395" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F395" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G395" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>69</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>RERUN</t>
+        </is>
+      </c>
+    </row>
+    <row r="397"/>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>70</v>
+      </c>
+      <c r="B398" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D398" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E398" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F398" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G398" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>70</v>
+      </c>
+      <c r="B399" t="n">
+        <v>2</v>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="D399" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E399" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F399" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>70</v>
+      </c>
+      <c r="B400" t="n">
+        <v>3</v>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E400" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F400" s="1" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="G400" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>70</v>
+      </c>
+      <c r="B401" t="n">
+        <v>4</v>
+      </c>
+      <c r="C401" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G401" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>70</v>
+      </c>
+      <c r="B402" t="n">
+        <v>5</v>
+      </c>
+      <c r="C402" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G402" s="3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>70</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>FLUFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="404"/>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>71</v>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D405" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E405" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F405" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G405" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>72</v>
+      </c>
+      <c r="B407" t="n">
+        <v>1</v>
+      </c>
+      <c r="C407" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D407" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E407" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F407" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>72</v>
+      </c>
+      <c r="B408" t="n">
+        <v>2</v>
+      </c>
+      <c r="C408" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G408" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>72</v>
+      </c>
+      <c r="B409" t="n">
+        <v>3</v>
+      </c>
+      <c r="C409" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F409" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G409" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>72</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>HELIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="411"/>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>73</v>
+      </c>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E412" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F412" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G412" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>73</v>
+      </c>
+      <c r="B413" t="n">
+        <v>2</v>
+      </c>
+      <c r="C413" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F413" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G413" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>73</v>
+      </c>
+      <c r="B414" t="n">
+        <v>3</v>
+      </c>
+      <c r="C414" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F414" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G414" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>73</v>
+      </c>
+      <c r="B415" t="n">
+        <v>4</v>
+      </c>
+      <c r="C415" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F415" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G415" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>73</v>
+      </c>
+      <c r="B416" t="n">
+        <v>5</v>
+      </c>
+      <c r="C416" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F416" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G416" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>73</v>
+      </c>
+      <c r="B417" t="n">
+        <v>6</v>
+      </c>
+      <c r="C417" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F417" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G417" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>73</v>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>GRAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="419"/>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>74</v>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E420" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F420" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G420" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="421"/>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>75</v>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D422" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F422" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G422" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>75</v>
+      </c>
+      <c r="B423" t="n">
+        <v>2</v>
+      </c>
+      <c r="C423" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D423" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G423" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>75</v>
+      </c>
+      <c r="B424" t="n">
+        <v>3</v>
+      </c>
+      <c r="C424" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F424" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G424" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>75</v>
+      </c>
+      <c r="B425" t="n">
+        <v>4</v>
+      </c>
+      <c r="C425" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F425" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G425" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>75</v>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>BOUGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="427"/>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>76</v>
+      </c>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
+      <c r="C428" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E428" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F428" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G428" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>76</v>
+      </c>
+      <c r="B429" t="n">
+        <v>2</v>
+      </c>
+      <c r="C429" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D429" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E429" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F429" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G429" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>76</v>
+      </c>
+      <c r="B430" t="n">
+        <v>3</v>
+      </c>
+      <c r="C430" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D430" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E430" s="1" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F430" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G430" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>76</v>
+      </c>
+      <c r="B431" t="n">
+        <v>4</v>
+      </c>
+      <c r="C431" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D431" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E431" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F431" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G431" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>76</v>
+      </c>
+      <c r="B432" t="n">
+        <v>5</v>
+      </c>
+      <c r="C432" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D432" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E432" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F432" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G432" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>76</v>
+      </c>
+      <c r="B433" t="n">
+        <v>6</v>
+      </c>
+      <c r="C433" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D433" s="3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E433" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F433" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G433" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>76</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>CREME</t>
+        </is>
+      </c>
+    </row>
+    <row r="435"/>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>77</v>
+      </c>
+      <c r="B436" t="n">
+        <v>1</v>
+      </c>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D436" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E436" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F436" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>77</v>
+      </c>
+      <c r="B437" t="n">
+        <v>2</v>
+      </c>
+      <c r="C437" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D437" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E437" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F437" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G437" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>77</v>
+      </c>
+      <c r="B438" t="n">
+        <v>3</v>
+      </c>
+      <c r="C438" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D438" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E438" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F438" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G438" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>77</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>ALLEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="440"/>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>78</v>
+      </c>
+      <c r="B441" t="n">
+        <v>1</v>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D441" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F441" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G441" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>78</v>
+      </c>
+      <c r="B442" t="n">
+        <v>2</v>
+      </c>
+      <c r="C442" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E442" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>78</v>
+      </c>
+      <c r="B443" t="n">
+        <v>3</v>
+      </c>
+      <c r="C443" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D443" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E443" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F443" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G443" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>78</v>
+      </c>
+      <c r="B444" t="n">
+        <v>4</v>
+      </c>
+      <c r="C444" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D444" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E444" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F444" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G444" s="3" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>78</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>TOPAZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="446"/>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>79</v>
+      </c>
+      <c r="B447" t="n">
+        <v>1</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="448"/>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>80</v>
+      </c>
+      <c r="B449" t="n">
+        <v>1</v>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D449" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E449" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F449" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>80</v>
+      </c>
+      <c r="B450" t="n">
+        <v>2</v>
+      </c>
+      <c r="C450" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D450" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E450" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F450" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G450" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>80</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>LEAST</t>
+        </is>
+      </c>
+    </row>
+    <row r="452"/>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>81</v>
+      </c>
+      <c r="B453" t="n">
+        <v>1</v>
+      </c>
+      <c r="C453" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D453" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E453" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F453" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>81</v>
+      </c>
+      <c r="B454" t="n">
+        <v>2</v>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D454" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E454" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G454" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>81</v>
+      </c>
+      <c r="B455" t="n">
+        <v>3</v>
+      </c>
+      <c r="C455" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D455" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E455" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G455" s="1" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>81</v>
+      </c>
+      <c r="B456" t="n">
+        <v>4</v>
+      </c>
+      <c r="C456" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D456" s="1" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F456" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G456" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>81</v>
+      </c>
+      <c r="B457" t="n">
+        <v>5</v>
+      </c>
+      <c r="C457" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D457" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E457" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F457" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G457" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>81</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>EVENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="459"/>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>82</v>
+      </c>
+      <c r="B460" t="n">
+        <v>1</v>
+      </c>
+      <c r="C460" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D460" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E460" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F460" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>82</v>
+      </c>
+      <c r="B461" t="n">
+        <v>2</v>
+      </c>
+      <c r="C461" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D461" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E461" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G461" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>82</v>
+      </c>
+      <c r="B462" t="n">
+        <v>3</v>
+      </c>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E462" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F462" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G462" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>82</v>
+      </c>
+      <c r="B463" t="n">
+        <v>4</v>
+      </c>
+      <c r="C463" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D463" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="E463" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F463" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G463" s="3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>82</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>TEETH</t>
+        </is>
+      </c>
+    </row>
+    <row r="465"/>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>83</v>
+      </c>
+      <c r="B466" t="n">
+        <v>1</v>
+      </c>
+      <c r="C466" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D466" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E466" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G466" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>83</v>
+      </c>
+      <c r="B467" t="n">
+        <v>2</v>
+      </c>
+      <c r="C467" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D467" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E467" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F467" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>83</v>
+      </c>
+      <c r="B468" t="n">
+        <v>3</v>
+      </c>
+      <c r="C468" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F468" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G468" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>83</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>ASSAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="470"/>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>84</v>
+      </c>
+      <c r="B471" t="n">
+        <v>1</v>
+      </c>
+      <c r="C471" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D471" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E471" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F471" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G471" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>84</v>
+      </c>
+      <c r="B472" t="n">
+        <v>2</v>
+      </c>
+      <c r="C472" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D472" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E472" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F472" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G472" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>84</v>
+      </c>
+      <c r="B473" t="n">
+        <v>3</v>
+      </c>
+      <c r="C473" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D473" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E473" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F473" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G473" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>84</v>
+      </c>
+      <c r="B474" t="n">
+        <v>4</v>
+      </c>
+      <c r="C474" s="3" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F474" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G474" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>84</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>GLOOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="476"/>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>85</v>
+      </c>
+      <c r="B477" t="n">
+        <v>1</v>
+      </c>
+      <c r="C477" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D477" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F477" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G477" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>85</v>
+      </c>
+      <c r="B478" t="n">
+        <v>2</v>
+      </c>
+      <c r="C478" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D478" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E478" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="F478" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G478" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>85</v>
+      </c>
+      <c r="B479" t="n">
+        <v>3</v>
+      </c>
+      <c r="C479" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D479" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E479" s="3" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F479" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G479" s="3" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>85</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>IDIOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="481"/>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>86</v>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D482" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E482" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F482" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>86</v>
+      </c>
+      <c r="B483" t="n">
+        <v>2</v>
+      </c>
+      <c r="C483" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D483" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E483" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F483" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G483" s="1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>86</v>
+      </c>
+      <c r="B484" t="n">
+        <v>3</v>
+      </c>
+      <c r="C484" s="1" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="D484" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F484" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>86</v>
+      </c>
+      <c r="B485" t="n">
+        <v>4</v>
+      </c>
+      <c r="C485" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F485" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G485" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>86</v>
+      </c>
+      <c r="B486" t="n">
+        <v>5</v>
+      </c>
+      <c r="C486" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F486" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G486" s="3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>86</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>MODEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>87</v>
+      </c>
+      <c r="B489" t="n">
+        <v>1</v>
+      </c>
+      <c r="C489" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D489" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E489" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F489" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G489" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>87</v>
+      </c>
+      <c r="B490" t="n">
+        <v>2</v>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E490" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F490" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G490" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>87</v>
+      </c>
+      <c r="B491" t="n">
+        <v>3</v>
+      </c>
+      <c r="C491" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D491" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E491" s="3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F491" s="3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G491" s="3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>87</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>ANSWER</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>ENSUE</t>
         </is>
       </c>
     </row>
